--- a/Methanol/Patagonien_Methanol_1_DAC_Greenfield/Datenbank.xlsx
+++ b/Methanol/Patagonien_Methanol_1_DAC_Greenfield/Datenbank.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Methanol_DAC_Greenfield_Patagonien\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Patagonien_Methanol_1_DAC_Greenfield\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE6F856-A66B-47DE-A702-F8964D4A7F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3A1B25-69B1-44D8-843C-067EE2D7B619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-6885" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
     <sheet name="Ergebnisse" sheetId="5" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="9.8999999999999999E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="364">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1285,6 +1285,12 @@
   </si>
   <si>
     <t>kg</t>
+  </si>
+  <si>
+    <t>Landesspezifischer Zinssatz</t>
+  </si>
+  <si>
+    <t>wacc_change</t>
   </si>
 </sst>
 </file>
@@ -1829,23 +1835,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G72"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G73"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="21" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" customWidth="1"/>
+    <col min="9" max="9" width="13.90625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -1866,7 +1872,7 @@
       </c>
       <c r="G1" s="21"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="30" t="s">
         <v>70</v>
       </c>
@@ -1886,7 +1892,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
       <c r="B3" s="38"/>
       <c r="C3" t="s">
@@ -1902,7 +1908,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="31"/>
       <c r="B4" s="38"/>
       <c r="C4" t="s">
@@ -1918,7 +1924,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="31"/>
       <c r="B5" s="38"/>
       <c r="C5" t="s">
@@ -1934,7 +1940,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="31"/>
       <c r="B6" s="38"/>
       <c r="C6" t="s">
@@ -1950,7 +1956,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="31"/>
       <c r="B7" s="38"/>
       <c r="C7" t="s">
@@ -1966,7 +1972,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="31"/>
       <c r="B8" s="41" t="s">
         <v>228</v>
@@ -1984,7 +1990,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="31"/>
       <c r="B9" s="38"/>
       <c r="C9" t="s">
@@ -2000,7 +2006,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="31"/>
       <c r="B10" s="38"/>
       <c r="C10" t="s">
@@ -2016,7 +2022,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="31"/>
       <c r="B11" s="38"/>
       <c r="C11" t="s">
@@ -2032,7 +2038,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="31"/>
       <c r="B12" s="38"/>
       <c r="C12" t="s">
@@ -2048,7 +2054,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="31"/>
       <c r="B13" s="38"/>
       <c r="C13" t="s">
@@ -2064,7 +2070,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="31"/>
       <c r="B14" s="38"/>
       <c r="C14" t="s">
@@ -2080,7 +2086,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="31"/>
       <c r="B15" s="42"/>
       <c r="C15" s="13" t="s">
@@ -2096,7 +2102,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="31"/>
       <c r="B16" s="41" t="s">
         <v>284</v>
@@ -2114,7 +2120,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="31"/>
       <c r="B17" s="38"/>
       <c r="C17" t="s">
@@ -2130,7 +2136,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="31"/>
       <c r="B18" s="38"/>
       <c r="C18" t="s">
@@ -2146,7 +2152,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="31"/>
       <c r="B19" s="38"/>
       <c r="C19" t="s">
@@ -2162,7 +2168,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="31"/>
       <c r="B20" s="38"/>
       <c r="C20" t="s">
@@ -2178,7 +2184,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="31"/>
       <c r="B21" s="42"/>
       <c r="C21" s="13" t="s">
@@ -2194,7 +2200,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="31"/>
       <c r="B22" s="34" t="s">
         <v>227</v>
@@ -2212,7 +2218,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="31"/>
       <c r="B23" s="34"/>
       <c r="C23" t="s">
@@ -2228,7 +2234,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="31"/>
       <c r="B24" s="34"/>
       <c r="C24" t="s">
@@ -2244,7 +2250,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="31"/>
       <c r="B25" s="34"/>
       <c r="C25" t="s">
@@ -2260,7 +2266,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="31"/>
       <c r="B26" s="34"/>
       <c r="C26" t="s">
@@ -2276,7 +2282,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="31"/>
       <c r="B27" s="34"/>
       <c r="C27" t="s">
@@ -2292,7 +2298,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="30" t="s">
         <v>71</v>
       </c>
@@ -2312,7 +2318,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="31"/>
       <c r="B29" s="34"/>
       <c r="C29" t="s">
@@ -2328,7 +2334,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="31"/>
       <c r="B30" s="34"/>
       <c r="C30" t="s">
@@ -2344,7 +2350,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="31"/>
       <c r="B31" s="34"/>
       <c r="C31" t="s">
@@ -2360,7 +2366,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="31"/>
       <c r="B32" s="34"/>
       <c r="C32" t="s">
@@ -2376,7 +2382,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="31"/>
       <c r="B33" s="34"/>
       <c r="C33" t="s">
@@ -2392,7 +2398,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="31"/>
       <c r="B34" s="34"/>
       <c r="C34" t="s">
@@ -2408,7 +2414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="31"/>
       <c r="B35" s="35"/>
       <c r="C35" s="13" t="s">
@@ -2424,7 +2430,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="31"/>
       <c r="B36" s="36" t="s">
         <v>329</v>
@@ -2442,7 +2448,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="31"/>
       <c r="B37" s="34"/>
       <c r="C37" t="s">
@@ -2458,7 +2464,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="31"/>
       <c r="B38" s="34"/>
       <c r="C38" t="s">
@@ -2474,7 +2480,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="31"/>
       <c r="B39" s="34"/>
       <c r="C39" t="s">
@@ -2490,7 +2496,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="31"/>
       <c r="B40" s="34"/>
       <c r="C40" t="s">
@@ -2506,7 +2512,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="31"/>
       <c r="B41" s="34"/>
       <c r="C41" t="s">
@@ -2522,7 +2528,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="31"/>
       <c r="B42" s="34"/>
       <c r="C42" t="s">
@@ -2538,7 +2544,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="31"/>
       <c r="B43" s="34"/>
       <c r="C43" s="13" t="s">
@@ -2554,7 +2560,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="31"/>
       <c r="B44" s="36" t="s">
         <v>201</v>
@@ -2572,7 +2578,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="31"/>
       <c r="B45" s="38"/>
       <c r="C45" t="s">
@@ -2589,7 +2595,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="31"/>
       <c r="B46" s="38"/>
       <c r="C46" t="s">
@@ -2605,7 +2611,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="31"/>
       <c r="B47" s="38"/>
       <c r="C47" t="s">
@@ -2621,7 +2627,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="31"/>
       <c r="B48" s="38"/>
       <c r="C48" t="s">
@@ -2637,7 +2643,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="31"/>
       <c r="B49" s="38"/>
       <c r="C49" t="s">
@@ -2653,7 +2659,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="31"/>
       <c r="B50" s="38"/>
       <c r="C50" t="s">
@@ -2669,7 +2675,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="31"/>
       <c r="B51" s="38"/>
       <c r="C51" t="s">
@@ -2685,7 +2691,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="31"/>
       <c r="B52" s="38"/>
       <c r="C52" t="s">
@@ -2701,7 +2707,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="32"/>
       <c r="B53" s="39"/>
       <c r="C53" s="17" t="s">
@@ -2717,7 +2723,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="30" t="s">
         <v>72</v>
       </c>
@@ -2737,7 +2743,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="31"/>
       <c r="B55" s="36" t="s">
         <v>4</v>
@@ -2755,7 +2761,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="31"/>
       <c r="B56" s="34"/>
       <c r="C56" t="s">
@@ -2771,7 +2777,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="31"/>
       <c r="B57" s="34"/>
       <c r="C57" t="s">
@@ -2787,7 +2793,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="31"/>
       <c r="B58" s="34"/>
       <c r="C58" t="s">
@@ -2803,7 +2809,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="31"/>
       <c r="B59" s="34"/>
       <c r="C59" t="s">
@@ -2819,7 +2825,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="31"/>
       <c r="B60" s="34"/>
       <c r="C60" t="s">
@@ -2835,7 +2841,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="31"/>
       <c r="B61" s="35"/>
       <c r="C61" s="13" t="s">
@@ -2851,7 +2857,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="31"/>
       <c r="B62" s="36" t="s">
         <v>5</v>
@@ -2869,7 +2875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="31"/>
       <c r="B63" s="34"/>
       <c r="C63" t="s">
@@ -2885,7 +2891,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="31"/>
       <c r="B64" s="34"/>
       <c r="C64" t="s">
@@ -2901,7 +2907,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="31"/>
       <c r="B65" s="34"/>
       <c r="C65" t="s">
@@ -2917,7 +2923,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="31"/>
       <c r="B66" s="34"/>
       <c r="C66" t="s">
@@ -2933,7 +2939,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="31"/>
       <c r="B67" s="34"/>
       <c r="C67" t="s">
@@ -2949,7 +2955,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="32"/>
       <c r="B68" s="37"/>
       <c r="C68" s="17" t="s">
@@ -2965,7 +2971,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="30" t="s">
         <v>76</v>
       </c>
@@ -2985,7 +2991,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="31"/>
       <c r="B70" s="21" t="s">
         <v>313</v>
@@ -3003,7 +3009,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="31"/>
       <c r="B71" s="27" t="s">
         <v>79</v>
@@ -3021,7 +3027,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="32"/>
       <c r="B72" s="3" t="s">
         <v>272</v>
@@ -3037,6 +3043,26 @@
       </c>
       <c r="F72" s="17" t="s">
         <v>286</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" t="s">
+        <v>362</v>
+      </c>
+      <c r="D73" t="s">
+        <v>363</v>
+      </c>
+      <c r="E73" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F73" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3064,17 +3090,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
   <dimension ref="A1:F141"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.81640625" customWidth="1"/>
+    <col min="5" max="5" width="46.08984375" customWidth="1"/>
+    <col min="6" max="6" width="37.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -3094,7 +3120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="30" t="s">
         <v>70</v>
       </c>
@@ -3112,7 +3138,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
       <c r="B3" s="38"/>
       <c r="C3" t="s">
@@ -3126,7 +3152,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="31"/>
       <c r="B4" s="38"/>
       <c r="C4" t="s">
@@ -3140,7 +3166,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="31"/>
       <c r="B5" s="38"/>
       <c r="C5" t="s">
@@ -3154,7 +3180,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="31"/>
       <c r="B6" s="38"/>
       <c r="C6" t="s">
@@ -3168,7 +3194,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="31"/>
       <c r="B7" s="38"/>
       <c r="C7" t="s">
@@ -3182,7 +3208,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="31"/>
       <c r="B8" s="38"/>
       <c r="C8" t="s">
@@ -3196,7 +3222,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="31"/>
       <c r="B9" s="38"/>
       <c r="C9" t="s">
@@ -3210,7 +3236,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="31"/>
       <c r="B10" s="38"/>
       <c r="C10" t="s">
@@ -3224,12 +3250,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="31"/>
       <c r="B11" s="38"/>
       <c r="E11" s="9"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="31"/>
       <c r="B12" s="41" t="s">
         <v>228</v>
@@ -3245,7 +3271,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="31"/>
       <c r="B13" s="38"/>
       <c r="C13" t="s">
@@ -3259,7 +3285,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="31"/>
       <c r="B14" s="38"/>
       <c r="C14" t="s">
@@ -3273,7 +3299,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="31"/>
       <c r="B15" s="38"/>
       <c r="C15" t="s">
@@ -3287,7 +3313,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="31"/>
       <c r="B16" s="38"/>
       <c r="C16" t="s">
@@ -3301,7 +3327,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="31"/>
       <c r="B17" s="38"/>
       <c r="C17" t="s">
@@ -3315,7 +3341,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="31"/>
       <c r="B18" s="38"/>
       <c r="C18" t="s">
@@ -3329,7 +3355,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="31"/>
       <c r="B19" s="38"/>
       <c r="C19" t="s">
@@ -3343,7 +3369,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="31"/>
       <c r="B20" s="38"/>
       <c r="C20" t="s">
@@ -3357,7 +3383,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="31"/>
       <c r="B21" s="38"/>
       <c r="C21" t="s">
@@ -3371,7 +3397,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="31"/>
       <c r="B22" s="42"/>
       <c r="C22" s="13"/>
@@ -3379,7 +3405,7 @@
       <c r="E22" s="14"/>
       <c r="F22" s="13"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="31"/>
       <c r="B23" s="41" t="s">
         <v>284</v>
@@ -3395,7 +3421,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="31"/>
       <c r="B24" s="38"/>
       <c r="C24" t="s">
@@ -3409,7 +3435,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="31"/>
       <c r="B25" s="38"/>
       <c r="C25" t="s">
@@ -3423,7 +3449,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="31"/>
       <c r="B26" s="38"/>
       <c r="C26" t="s">
@@ -3437,7 +3463,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="31"/>
       <c r="B27" s="38"/>
       <c r="C27" t="s">
@@ -3451,7 +3477,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="31"/>
       <c r="B28" s="38"/>
       <c r="C28" t="s">
@@ -3465,7 +3491,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="31"/>
       <c r="B29" s="38"/>
       <c r="C29" t="s">
@@ -3479,7 +3505,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="31"/>
       <c r="B30" s="38"/>
       <c r="C30" t="s">
@@ -3493,7 +3519,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="31"/>
       <c r="B31" s="38"/>
       <c r="C31" t="s">
@@ -3507,7 +3533,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="31"/>
       <c r="B32" s="42"/>
       <c r="C32" s="13"/>
@@ -3515,7 +3541,7 @@
       <c r="E32" s="14"/>
       <c r="F32" s="13"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="31"/>
       <c r="B33" s="34" t="s">
         <v>227</v>
@@ -3531,7 +3557,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="31"/>
       <c r="B34" s="34"/>
       <c r="C34" t="s">
@@ -3545,7 +3571,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="31"/>
       <c r="B35" s="34"/>
       <c r="C35" t="s">
@@ -3559,7 +3585,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="31"/>
       <c r="B36" s="34"/>
       <c r="C36" t="s">
@@ -3573,7 +3599,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="31"/>
       <c r="B37" s="34"/>
       <c r="C37" t="s">
@@ -3587,7 +3613,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="31"/>
       <c r="B38" s="34"/>
       <c r="C38" t="s">
@@ -3601,7 +3627,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="31"/>
       <c r="B39" s="34"/>
       <c r="C39" t="s">
@@ -3615,7 +3641,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="31"/>
       <c r="B40" s="34"/>
       <c r="C40" t="s">
@@ -3629,7 +3655,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="31"/>
       <c r="B41" s="34"/>
       <c r="C41" t="s">
@@ -3643,7 +3669,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="31"/>
       <c r="B42" s="34"/>
       <c r="C42" t="s">
@@ -3657,12 +3683,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="31"/>
       <c r="B43" s="34"/>
       <c r="E43" s="9"/>
     </row>
-    <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="30" t="s">
         <v>71</v>
       </c>
@@ -3680,7 +3706,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="31"/>
       <c r="B45" s="34"/>
       <c r="C45" t="s">
@@ -3694,7 +3720,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="31"/>
       <c r="B46" s="34"/>
       <c r="C46" t="s">
@@ -3708,7 +3734,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="31"/>
       <c r="B47" s="34"/>
       <c r="C47" t="s">
@@ -3722,7 +3748,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="31"/>
       <c r="B48" s="34"/>
       <c r="C48" t="s">
@@ -3736,7 +3762,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="31"/>
       <c r="B49" s="34"/>
       <c r="C49" t="s">
@@ -3750,7 +3776,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="31"/>
       <c r="B50" s="34"/>
       <c r="C50" t="s">
@@ -3764,7 +3790,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="31"/>
       <c r="B51" s="34"/>
       <c r="C51" t="s">
@@ -3778,7 +3804,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="31"/>
       <c r="B52" s="34"/>
       <c r="C52" t="s">
@@ -3792,7 +3818,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="31"/>
       <c r="B53" s="35"/>
       <c r="C53" s="13"/>
@@ -3800,7 +3826,7 @@
       <c r="E53" s="14"/>
       <c r="F53" s="13"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="31"/>
       <c r="B54" s="34" t="s">
         <v>329</v>
@@ -3816,7 +3842,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="31"/>
       <c r="B55" s="34"/>
       <c r="C55" t="s">
@@ -3830,7 +3856,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="31"/>
       <c r="B56" s="34"/>
       <c r="C56" t="s">
@@ -3844,7 +3870,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="31"/>
       <c r="B57" s="34"/>
       <c r="C57" t="s">
@@ -3858,7 +3884,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="31"/>
       <c r="B58" s="34"/>
       <c r="C58" t="s">
@@ -3872,7 +3898,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="31"/>
       <c r="B59" s="34"/>
       <c r="C59" t="s">
@@ -3886,7 +3912,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="31"/>
       <c r="B60" s="34"/>
       <c r="C60" t="s">
@@ -3900,7 +3926,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="31"/>
       <c r="B61" s="34"/>
       <c r="C61" t="s">
@@ -3914,7 +3940,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="31"/>
       <c r="B62" s="34"/>
       <c r="C62" t="s">
@@ -3928,12 +3954,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="31"/>
       <c r="B63" s="35"/>
       <c r="E63" s="9"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="31"/>
       <c r="B64" s="36" t="s">
         <v>6</v>
@@ -3949,7 +3975,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="31"/>
       <c r="B65" s="34"/>
       <c r="C65" t="s">
@@ -3963,7 +3989,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="31"/>
       <c r="B66" s="38"/>
       <c r="C66" t="s">
@@ -3977,7 +4003,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="31"/>
       <c r="B67" s="38"/>
       <c r="C67" t="s">
@@ -3991,7 +4017,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="31"/>
       <c r="B68" s="38"/>
       <c r="C68" t="s">
@@ -4005,7 +4031,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="31"/>
       <c r="B69" s="38"/>
       <c r="C69" t="s">
@@ -4019,7 +4045,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="31"/>
       <c r="B70" s="38"/>
       <c r="C70" t="s">
@@ -4033,7 +4059,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="31"/>
       <c r="B71" s="38"/>
       <c r="C71" t="s">
@@ -4047,7 +4073,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="31"/>
       <c r="B72" s="38"/>
       <c r="C72" t="s">
@@ -4061,7 +4087,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="31"/>
       <c r="B73" s="38"/>
       <c r="C73" t="s">
@@ -4075,7 +4101,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="31"/>
       <c r="B74" s="38"/>
       <c r="C74" t="s">
@@ -4089,7 +4115,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="32"/>
       <c r="B75" s="39"/>
       <c r="C75" s="17"/>
@@ -4097,7 +4123,7 @@
       <c r="E75" s="18"/>
       <c r="F75" s="17"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="30" t="s">
         <v>72</v>
       </c>
@@ -4115,7 +4141,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="31"/>
       <c r="B77" s="38"/>
       <c r="C77" t="s">
@@ -4129,12 +4155,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="31"/>
       <c r="B78" s="42"/>
       <c r="E78" s="7"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="31"/>
       <c r="B79" s="36" t="s">
         <v>4</v>
@@ -4150,7 +4176,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="31"/>
       <c r="B80" s="34"/>
       <c r="C80" t="s">
@@ -4164,7 +4190,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="31"/>
       <c r="B81" s="34"/>
       <c r="C81" t="s">
@@ -4178,7 +4204,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="31"/>
       <c r="B82" s="34"/>
       <c r="C82" t="s">
@@ -4192,7 +4218,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="31"/>
       <c r="B83" s="34"/>
       <c r="C83" t="s">
@@ -4206,7 +4232,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="31"/>
       <c r="B84" s="34"/>
       <c r="C84" t="s">
@@ -4220,7 +4246,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="31"/>
       <c r="B85" s="34"/>
       <c r="C85" t="s">
@@ -4234,7 +4260,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="31"/>
       <c r="B86" s="34"/>
       <c r="C86" t="s">
@@ -4248,7 +4274,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="31"/>
       <c r="B87" s="34"/>
       <c r="C87" t="s">
@@ -4262,11 +4288,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="31"/>
       <c r="B88" s="35"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="31"/>
       <c r="B89" s="36" t="s">
         <v>5</v>
@@ -4282,7 +4308,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="31"/>
       <c r="B90" s="34"/>
       <c r="C90" t="s">
@@ -4296,7 +4322,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="31"/>
       <c r="B91" s="34"/>
       <c r="C91" t="s">
@@ -4310,7 +4336,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="31"/>
       <c r="B92" s="34"/>
       <c r="C92" t="s">
@@ -4324,7 +4350,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="31"/>
       <c r="B93" s="34"/>
       <c r="C93" t="s">
@@ -4338,7 +4364,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="31"/>
       <c r="B94" s="34"/>
       <c r="C94" t="s">
@@ -4352,7 +4378,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="31"/>
       <c r="B95" s="34"/>
       <c r="C95" t="s">
@@ -4366,7 +4392,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="31"/>
       <c r="B96" s="34"/>
       <c r="C96" t="s">
@@ -4380,7 +4406,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="31"/>
       <c r="B97" s="34"/>
       <c r="C97" t="s">
@@ -4394,11 +4420,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="32"/>
       <c r="B98" s="37"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="30" t="s">
         <v>76</v>
       </c>
@@ -4416,7 +4442,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="31"/>
       <c r="B100" s="38"/>
       <c r="C100" t="s">
@@ -4430,7 +4456,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="31"/>
       <c r="B101" s="42"/>
       <c r="C101" s="13"/>
@@ -4438,7 +4464,7 @@
       <c r="E101" s="14"/>
       <c r="F101" s="13"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="31"/>
       <c r="B102" s="41" t="s">
         <v>317</v>
@@ -4454,7 +4480,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="31"/>
       <c r="B103" s="38"/>
       <c r="C103" t="s">
@@ -4468,12 +4494,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="31"/>
       <c r="B104" s="42"/>
       <c r="E104" s="9"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="31"/>
       <c r="B105" s="41" t="s">
         <v>79</v>
@@ -4489,7 +4515,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="31"/>
       <c r="B106" s="38"/>
       <c r="C106" t="s">
@@ -4503,7 +4529,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="31"/>
       <c r="B107" s="42"/>
       <c r="C107" s="13"/>
@@ -4511,7 +4537,7 @@
       <c r="E107" s="14"/>
       <c r="F107" s="13"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="31"/>
       <c r="B108" s="41" t="s">
         <v>272</v>
@@ -4527,7 +4553,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="31"/>
       <c r="B109" s="38"/>
       <c r="C109" t="s">
@@ -4541,7 +4567,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="32"/>
       <c r="B110" s="39"/>
       <c r="C110" s="17"/>
@@ -4549,7 +4575,7 @@
       <c r="E110" s="18"/>
       <c r="F110" s="17"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="30" t="s">
         <v>163</v>
       </c>
@@ -4567,7 +4593,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="31"/>
       <c r="B112" s="38"/>
       <c r="C112" t="s">
@@ -4580,7 +4606,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="31"/>
       <c r="B113" s="42"/>
       <c r="C113" s="13"/>
@@ -4588,7 +4614,7 @@
       <c r="E113" s="13"/>
       <c r="F113" s="13"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="31"/>
       <c r="B114" s="41" t="s">
         <v>183</v>
@@ -4603,7 +4629,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="31"/>
       <c r="B115" s="38"/>
       <c r="C115" t="s">
@@ -4616,7 +4642,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="31"/>
       <c r="B116" s="38"/>
       <c r="C116" t="s">
@@ -4629,7 +4655,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="31"/>
       <c r="B117" s="38"/>
       <c r="C117" t="s">
@@ -4642,7 +4668,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="31"/>
       <c r="B118" s="38"/>
       <c r="C118" t="s">
@@ -4655,7 +4681,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="31"/>
       <c r="B119" s="38"/>
       <c r="C119" t="s">
@@ -4668,11 +4694,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="31"/>
       <c r="B120" s="38"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="31"/>
       <c r="B121" s="41" t="s">
         <v>206</v>
@@ -4688,7 +4714,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="31"/>
       <c r="B122" s="38"/>
       <c r="C122" t="s">
@@ -4701,7 +4727,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="31"/>
       <c r="B123" s="38"/>
       <c r="C123" t="s">
@@ -4714,7 +4740,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="31"/>
       <c r="B124" s="38"/>
       <c r="C124" t="s">
@@ -4727,7 +4753,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="31"/>
       <c r="B125" s="38"/>
       <c r="C125" t="s">
@@ -4740,7 +4766,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="31"/>
       <c r="B126" s="38"/>
       <c r="C126" t="s">
@@ -4753,7 +4779,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="31"/>
       <c r="B127" s="38"/>
       <c r="C127" t="s">
@@ -4766,7 +4792,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="31"/>
       <c r="B128" s="38"/>
       <c r="C128" t="s">
@@ -4779,7 +4805,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="31"/>
       <c r="B129" s="38"/>
       <c r="C129" t="s">
@@ -4792,7 +4818,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="31"/>
       <c r="B130" s="38"/>
       <c r="C130" t="s">
@@ -4805,7 +4831,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="31"/>
       <c r="B131" s="38"/>
       <c r="C131" t="s">
@@ -4818,7 +4844,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="31"/>
       <c r="B132" s="38"/>
       <c r="C132" t="s">
@@ -4831,11 +4857,11 @@
         <v>213</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="31"/>
       <c r="B133" s="38"/>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="31"/>
       <c r="B134" s="41" t="s">
         <v>222</v>
@@ -4851,7 +4877,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="31"/>
       <c r="B135" s="38"/>
       <c r="C135" t="s">
@@ -4864,7 +4890,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="31"/>
       <c r="B136" s="38"/>
       <c r="C136" t="s">
@@ -4877,7 +4903,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="31"/>
       <c r="B137" s="38"/>
       <c r="C137" t="s">
@@ -4890,7 +4916,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="31"/>
       <c r="B138" s="38"/>
       <c r="C138" t="s">
@@ -4903,11 +4929,11 @@
         <v>213</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="31"/>
       <c r="B139" s="38"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="31"/>
       <c r="B140" s="41" t="s">
         <v>354</v>
@@ -4923,7 +4949,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="31"/>
       <c r="B141" s="38"/>
       <c r="C141" t="s">
